--- a/data/park/data.xlsx
+++ b/data/park/data.xlsx
@@ -7468,7 +7468,7 @@
         <v>http://www.takamatsujyo.com/</v>
       </c>
       <c r="H272" t="str">
-        <v>【入園料】大人（16～64歳）：200円　こども（6～15歳）：100円、【休園日】12月29日～31日、【開園時間】およそ日の出から日没まで。季節によって異なる。HP参照のこと。</v>
+        <v>【入園料】大人（18～64歳）：300円、【休園日】12月29日～31日、【開園時間】およそ日の出から日没まで。季節によって異なる。HP参照のこと。</v>
       </c>
     </row>
     <row r="273">
@@ -8215,6 +8215,15 @@
       <c r="E301" t="str">
         <v>高松市香西本町373-33</v>
       </c>
+      <c r="F301" t="str">
+        <v/>
+      </c>
+      <c r="G301" t="str">
+        <v/>
+      </c>
+      <c r="H301" t="str">
+        <v/>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="str">
@@ -8232,6 +8241,15 @@
       <c r="E302" t="str">
         <v>高松市香西本町373-14</v>
       </c>
+      <c r="F302" t="str">
+        <v/>
+      </c>
+      <c r="G302" t="str">
+        <v/>
+      </c>
+      <c r="H302" t="str">
+        <v/>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="str">
@@ -8249,6 +8267,15 @@
       <c r="E303" t="str">
         <v>高松市一宮町1049-3</v>
       </c>
+      <c r="F303" t="str">
+        <v/>
+      </c>
+      <c r="G303" t="str">
+        <v/>
+      </c>
+      <c r="H303" t="str">
+        <v/>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="str">
@@ -8266,6 +8293,15 @@
       <c r="E304" t="str">
         <v>高松市春日町841-5</v>
       </c>
+      <c r="F304" t="str">
+        <v/>
+      </c>
+      <c r="G304" t="str">
+        <v/>
+      </c>
+      <c r="H304" t="str">
+        <v/>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="str">
@@ -8283,6 +8319,15 @@
       <c r="E305" t="str">
         <v>高松市太田下町2323-1</v>
       </c>
+      <c r="F305" t="str">
+        <v/>
+      </c>
+      <c r="G305" t="str">
+        <v/>
+      </c>
+      <c r="H305" t="str">
+        <v/>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="str">
@@ -8300,6 +8345,15 @@
       <c r="E306" t="str">
         <v>高松市林町202-26</v>
       </c>
+      <c r="F306" t="str">
+        <v/>
+      </c>
+      <c r="G306" t="str">
+        <v/>
+      </c>
+      <c r="H306" t="str">
+        <v/>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="str">
@@ -8317,6 +8371,15 @@
       <c r="E307" t="str">
         <v>高松市林町1338-25</v>
       </c>
+      <c r="F307" t="str">
+        <v/>
+      </c>
+      <c r="G307" t="str">
+        <v/>
+      </c>
+      <c r="H307" t="str">
+        <v/>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="str">
@@ -8334,6 +8397,15 @@
       <c r="E308" t="str">
         <v>高松市仏生山町500-9</v>
       </c>
+      <c r="F308" t="str">
+        <v/>
+      </c>
+      <c r="G308" t="str">
+        <v/>
+      </c>
+      <c r="H308" t="str">
+        <v/>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="str">
@@ -8351,6 +8423,15 @@
       <c r="E309" t="str">
         <v>国分寺町新名1381-16</v>
       </c>
+      <c r="F309" t="str">
+        <v/>
+      </c>
+      <c r="G309" t="str">
+        <v/>
+      </c>
+      <c r="H309" t="str">
+        <v/>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="str">
@@ -8368,6 +8449,15 @@
       <c r="E310" t="str">
         <v>高松市亀水町458-3</v>
       </c>
+      <c r="F310" t="str">
+        <v/>
+      </c>
+      <c r="G310" t="str">
+        <v/>
+      </c>
+      <c r="H310" t="str">
+        <v/>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="str">
@@ -8384,6 +8474,15 @@
       </c>
       <c r="E311" t="str">
         <v>高松市御厩町771-1</v>
+      </c>
+      <c r="F311" t="str">
+        <v/>
+      </c>
+      <c r="G311" t="str">
+        <v/>
+      </c>
+      <c r="H311" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
